--- a/docs/ValueSet-BRFrequenciaUsoSubstancia.xlsx
+++ b/docs/ValueSet-BRFrequenciaUsoSubstancia.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -73,7 +73,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>null (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -106,19 +106,16 @@
     <t>MO</t>
   </si>
   <si>
-    <t>Mensalmente</t>
+    <t>monthly</t>
   </si>
   <si>
     <t>WK</t>
   </si>
   <si>
-    <t>Semanalmente</t>
+    <t>weekly</t>
   </si>
   <si>
     <t>QD</t>
-  </si>
-  <si>
-    <t>Diariamente</t>
   </si>
   <si>
     <t/>
@@ -436,23 +433,23 @@
         <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>36</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -471,28 +468,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
